--- a/Finanzen/Belegauswertung_2024/out/ergebnis_2024_monatlich_netto.xlsx
+++ b/Finanzen/Belegauswertung_2024/out/ergebnis_2024_monatlich_netto.xlsx
@@ -441,16 +441,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,20 +472,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -542,16 +548,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -572,20 +579,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -643,16 +655,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -673,20 +686,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -713,15 +731,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Lexoffice 11 24.pdf</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>5952.8657.2450 Haufe Service Center | GmbH Lexware Office L | 672bd1341a27de5c6e08d04e | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
@@ -748,15 +771,20 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Triathlon Miete.pdf</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Miete Postfach 10/24+11/24 | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
@@ -778,20 +806,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Ja (nur 1 Betrag, kein Netto/USt getrennt)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Finom 2024.pdf</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>PNL Fintech B.V.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Annual fee for Start plan (incl. VAT). | Subscription period: 29 Nov, 2024 - 28 Nov, | 2025</t>
         </is>
@@ -849,16 +882,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -879,20 +913,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -919,15 +958,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Lexoffice 12 24.pdf</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Haufe Service Center GmbH</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>5978.1098.7460 Haufe Service Center | GmbH lx2024120081302 KHYY-YNLG | Lexware Office L | 6753b36ad90b41fa05f86256 | IBAN: DE11672400390191115511 | BIC: COBADEFF</t>
         </is>
@@ -954,15 +998,20 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Triathlon Miete.pdf</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>TRIATHLON TRANSFER GMBH</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Miete Postfach | IBAN: DE38590501010067163204 | BIC: SAKSDE55XXX</t>
         </is>
@@ -1020,16 +1069,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1050,20 +1100,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -1121,16 +1176,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,20 +1207,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -1222,16 +1283,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1252,20 +1314,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -1323,16 +1390,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1353,20 +1421,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -1424,16 +1497,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1454,20 +1528,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -1525,16 +1604,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1555,20 +1635,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -1626,16 +1711,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1656,20 +1742,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>
@@ -1727,16 +1818,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1757,20 +1849,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Zaehlt zur Wertung?</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Beleg da?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beleg-Dateiname</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Verwendungszweck</t>
         </is>

--- a/Finanzen/Belegauswertung_2024/out/ergebnis_2024_monatlich_netto.xlsx
+++ b/Finanzen/Belegauswertung_2024/out/ergebnis_2024_monatlich_netto.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Oktober" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_November" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_Dezember" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_Jahresgesamt" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +43,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="3">
@@ -70,12 +75,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1063,6 +1069,323 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Monat</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Umsatz netto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Ausgabe netto</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Gewinn/Verlust</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Zahlungen ohne Beleg</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>01_Januar</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>02_Februar</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>03_Maerz</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>04_April</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>05_Mai</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>06_Juni</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>07_Juli</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>08_August</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>09_September</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10_Oktober</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11_November</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>134.91</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-134.91</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12_Dezember</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-34.95</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>GESAMTUMSATZ netto (Jahr):</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>GESAMTAUSGABEN netto (Jahr):</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>169.86</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>GESAMTNETTOGEWINN/-VERLUST (Jahr):</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-169.86</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>davon Zahlungen ohne Beleg (Jahr):</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
